--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -854,32 +854,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -887,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +915,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -998,7 +1006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1045,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1056,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1084,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1109,7 +1121,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1145,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1165,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1286,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1347,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1397,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1458,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1508,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1516,22 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1548,12 +1564,12 @@
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1567,7 +1583,7 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1603,7 +1619,788 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -891,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -940,12 +940,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -973,32 +973,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1006,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1030,17 +1034,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1050,13 +1054,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1114,12 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1121,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1160,14 +1168,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>92.0</t>
@@ -1175,7 +1183,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1211,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1236,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1260,33 +1272,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1314,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1347,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1371,33 +1391,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1497,7 +1521,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1508,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1608,7 +1632,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1619,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1647,32 +1671,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1680,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1704,33 +1732,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1841,7 +1873,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1952,7 +1984,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2063,7 +2095,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2174,7 +2206,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2284,12 +2316,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2297,22 +2329,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2350,7 +2382,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2364,7 +2396,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2400,7 +2432,915 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1560,32 +1560,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1593,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,17 +1621,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1637,13 +1641,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1689,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1708,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1757,12 +1765,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1934,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1973,7 +1981,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2045,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2156,7 +2164,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,7 +2275,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,7 +2390,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,7 +2501,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,7 +2616,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2662,7 +2670,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2842,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2888,7 +2896,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2957,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3003,7 +3011,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3072,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3175,7 +3183,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3219,13 +3227,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3298,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3335,12 +3347,123 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -891,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -930,17 +934,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1010,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1053,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1597,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1651,7 +1655,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,32 +1802,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1831,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1855,33 +1863,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1909,32 +1921,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1942,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1966,17 +1982,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1986,13 +2002,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2020,32 +2040,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2053,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2077,33 +2101,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2131,32 +2159,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2164,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2188,33 +2220,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2278,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2275,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2299,32 +2339,32 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2390,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2468,32 +2508,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2501,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2525,37 +2569,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3011,7 +3055,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3237,7 +3281,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3360,22 +3404,22 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3413,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3427,43 +3471,622 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>—/14</t>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1530,13 +1530,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1640,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1759,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1883,12 +1887,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2002,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2120,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2131,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2369,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,7 +2473,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2518,24 +2522,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2545,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2594,12 +2598,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2703,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2714,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2742,32 +2746,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -2775,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2799,33 +2807,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2853,32 +2865,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2886,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2910,37 +2926,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2968,32 +2984,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3001,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3025,37 +3045,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3083,32 +3103,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -3116,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3140,17 +3164,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3160,13 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3194,32 +3222,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -3227,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3251,37 +3283,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3309,32 +3341,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3342,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3366,37 +3402,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3424,32 +3460,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3457,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3481,17 +3521,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3501,12 +3541,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3539,32 +3579,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3572,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3596,17 +3640,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3616,17 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3726,7 +3770,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3741,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3856,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3971,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3979,22 +4023,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4032,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4046,47 +4090,963 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>91.5</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>4/14</t>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,13 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,17 +938,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,17 +1057,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1177,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1425,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1896,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2011,12 +2015,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2434,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,13 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,17 +2596,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2664,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2708,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2902,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3313,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3478,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -3497,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,12 +3554,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3589,24 +3597,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3616,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3665,12 +3673,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3698,32 +3706,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3731,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3755,17 +3767,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3775,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3813,32 +3825,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -3846,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,37 +3886,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3928,32 +3944,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3961,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3985,32 +4005,32 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4043,32 +4063,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4076,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4100,17 +4124,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4120,13 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4154,32 +4182,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4187,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4211,32 +4243,32 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4269,32 +4301,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4302,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4326,17 +4362,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4346,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4456,7 +4492,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4499,32 +4535,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -4532,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4556,37 +4596,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4701,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4816,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4931,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4939,22 +4979,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4987,12 +5027,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5006,47 +5046,737 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>13/14</t>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,14 +1886,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>85.5</t>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,17 +3430,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,14 +3544,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>85.5</t>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4311,24 +4311,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4420,32 +4420,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -4453,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4477,17 +4481,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4497,12 +4501,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4557,12 +4561,12 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4572,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4626,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4654,32 +4658,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4687,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4711,17 +4719,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4731,17 +4739,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4769,32 +4777,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -4802,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4826,32 +4838,32 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4884,32 +4896,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4917,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4941,17 +4957,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4961,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4999,32 +5015,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5032,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,17 +5076,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5076,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5114,32 +5134,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -5147,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5171,37 +5195,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5316,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5416,7 +5440,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5431,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5546,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5651,12 +5675,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5722,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5776,7 +5800,697 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,14 +1414,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>82.3</t>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,14 +1767,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>76.3</t>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,17 +2248,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,14 +3068,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>82.3</t>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,14 +3425,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>76.3</t>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,14 +4734,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>82.3</t>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,14 +4972,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>76.3</t>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5144,19 +5144,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5253,32 +5253,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5286,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5310,17 +5314,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5330,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5368,32 +5372,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -5401,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,17 +5433,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5445,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5491,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5516,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5540,17 +5552,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5560,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5598,32 +5610,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -5631,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,32 +5671,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5713,32 +5729,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -5746,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5770,17 +5790,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5790,12 +5810,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5828,32 +5848,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -5861,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5885,17 +5909,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5905,17 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5943,32 +5967,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5976,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6000,37 +6028,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6140,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6321,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6365,17 +6393,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6490,7 +6518,467 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,17 +819,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,17 +4139,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5858,24 +5858,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5977,24 +5977,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6086,32 +6086,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -6119,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6143,17 +6147,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6163,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6201,32 +6205,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6234,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,32 +6266,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6349,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6403,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6503,7 +6511,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6518,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6694,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6748,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6858,12 +6866,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6982,6 +6990,466 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6096,24 +6096,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6215,19 +6215,19 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6324,32 +6324,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -6357,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6381,17 +6385,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6401,12 +6405,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6439,32 +6443,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6472,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6496,17 +6504,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6516,17 +6524,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6702,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6756,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6871,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7047,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7096,7 +7104,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7162,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7216,7 +7224,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7392,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7436,17 +7444,132 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,14 +1057,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,14 +1648,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,14 +3306,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,22 +3425,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,14 +4258,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,14 +4853,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,14 +5567,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,14 +5924,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6453,24 +6453,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6562,32 +6562,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -6595,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6619,17 +6623,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6639,12 +6643,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6677,32 +6681,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6710,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6734,37 +6742,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6792,32 +6800,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6825,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6849,17 +6861,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6869,17 +6881,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6907,32 +6919,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6940,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,37 +6980,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7022,32 +7038,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7055,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7079,17 +7099,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7099,12 +7119,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7170,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7209,7 +7229,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7224,7 +7244,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7324,7 +7344,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7400,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7449,7 +7469,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7515,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7569,7 +7589,812 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
           <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,14 +1886,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,14 +2124,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,14 +2243,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,14 +3544,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,14 +3782,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,14 +3901,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,17 +4020,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,22 +4615,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,17 +4739,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,14 +5210,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,17 +5329,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,14 +5448,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,22 +5805,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,14 +6043,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,14 +6162,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,14 +6400,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6876,14 +6876,14 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>79.2</t>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6929,24 +6929,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7048,24 +7048,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7157,32 +7157,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7190,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7214,17 +7218,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7234,17 +7238,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7272,32 +7276,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -7305,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7329,17 +7337,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7349,12 +7357,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7387,32 +7395,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7420,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7444,17 +7456,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7464,17 +7476,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7502,32 +7514,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7535,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,32 +7575,32 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7617,32 +7633,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7650,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7674,17 +7694,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7694,17 +7714,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7732,32 +7752,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -7765,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7789,37 +7813,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7929,7 +7953,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7995,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8034,7 +8058,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8049,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8164,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8269,17 +8293,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8287,22 +8311,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A02126A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8335,12 +8359,12 @@
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8354,47 +8378,852 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>69.0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
         <is>
           <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,22 +3425,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,22 +5091,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6757,22 +6757,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6995,22 +6995,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,22 +7233,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7643,24 +7643,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7709,22 +7709,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7762,24 +7762,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7871,32 +7871,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7904,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7928,37 +7932,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8073,7 +8077,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8173,7 +8177,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8188,7 +8192,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8216,32 +8220,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8249,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8273,37 +8281,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,7 +8411,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8418,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8594,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8633,7 +8641,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8648,7 +8656,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8824,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8878,7 +8886,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9054,7 +9062,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9103,7 +9111,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9116,22 +9124,22 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9169,7 +9177,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9183,47 +9191,967 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>80.5</t>
         </is>
       </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>13/14</t>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>80.4</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,17 +2243,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,22 +2711,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,17 +2949,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,17 +3901,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,22 +4020,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,22 +4139,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,17 +4615,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,17 +5805,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,22 +6281,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,17 +6400,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,22 +6519,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7114,22 +7114,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,22 +7471,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,22 +7590,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7828,17 +7828,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,17 +8067,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8569,32 +8569,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8602,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8626,17 +8630,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8646,17 +8650,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8684,32 +8688,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8717,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8741,37 +8749,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8799,32 +8807,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8832,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8856,37 +8868,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8914,32 +8926,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -8947,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8971,32 +8987,32 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9029,32 +9045,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9062,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9086,32 +9106,32 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9144,32 +9164,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9177,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9201,37 +9225,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9331,7 +9355,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9374,32 +9398,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9407,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9431,17 +9459,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9451,17 +9479,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9561,7 +9589,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9576,7 +9604,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9637,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9691,7 +9719,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9806,7 +9834,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9921,7 +9949,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9982,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,17 +10054,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10044,22 +10072,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10097,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10141,17 +10169,822 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
+      <c r="AB83" s="2" t="inlineStr">
         <is>
           <t>80.6</t>
         </is>
       </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>14/14</t>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>80.4</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,22 +3425,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,22 +4020,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,22 +5091,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,22 +5210,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,22 +6162,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6643,17 +6643,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6757,22 +6757,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6881,12 +6881,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6995,22 +6995,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,22 +7233,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,22 +7590,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7709,22 +7709,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7947,22 +7947,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8182,17 +8182,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8296,22 +8296,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8411,22 +8411,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8883,22 +8883,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9283,32 +9283,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -9316,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9340,17 +9344,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9360,17 +9364,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9489,7 +9493,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9517,32 +9521,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -9550,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9574,17 +9582,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9594,17 +9602,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9632,32 +9640,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9665,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9689,37 +9701,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9747,32 +9759,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -9780,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9804,37 +9820,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9862,32 +9878,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9895,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9919,37 +9939,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9977,32 +9997,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10010,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10034,17 +10058,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10054,12 +10078,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10125,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10207,32 +10231,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10240,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10264,37 +10292,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10409,7 +10437,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10437,32 +10465,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10470,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10494,37 +10526,37 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10617,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10700,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10744,17 +10776,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10847,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10877,22 +10909,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10925,12 +10957,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10944,47 +10976,622 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB89" s="2" t="inlineStr">
-        <is>
-          <t>79.5</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
-        <is>
-          <t>7/14</t>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>81.6</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>82.6</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>75.1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,17 +2248,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9007,17 +9007,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10116,32 +10116,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10149,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10173,17 +10177,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10193,12 +10197,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10253,12 +10257,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10268,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10322,7 +10326,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10350,32 +10354,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -10383,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10407,17 +10415,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10427,17 +10435,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10475,24 +10483,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>65分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10502,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10551,12 +10559,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10732,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10786,7 +10794,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10886,7 +10894,7 @@
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
@@ -10962,7 +10970,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11077,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11192,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11307,7 +11315,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11361,7 +11369,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11430,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11537,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11586,12 +11594,127 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,17 +4739,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,22 +5924,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7476,17 +7476,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7714,17 +7714,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8177,22 +8177,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,17 +9245,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9597,22 +9597,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9721,17 +9721,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10376,12 +10376,12 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10592,32 +10592,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10625,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10649,17 +10653,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10669,17 +10673,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10707,32 +10711,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -10740,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10764,17 +10772,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10784,12 +10792,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10822,32 +10830,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -10855,7 +10867,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10879,17 +10891,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10899,7 +10911,7 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
@@ -10937,32 +10949,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10970,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10994,17 +11010,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11014,17 +11030,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11052,32 +11068,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11085,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11109,37 +11129,37 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11315,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11369,7 +11389,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11469,7 +11489,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11545,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11660,7 +11680,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11704,17 +11724,247 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB95" s="2" t="inlineStr">
-        <is>
-          <t>79.3</t>
-        </is>
-      </c>
-      <c r="AC95" s="2" t="inlineStr">
-        <is>
-          <t>6/14</t>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>82.6</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-182路.xlsx
+++ b/data/export/2026-10-22-182路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,17 +3430,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7952,17 +7952,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8301,17 +8301,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9840,17 +9840,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9959,17 +9959,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10316,17 +10316,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10840,24 +10840,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10959,12 +10959,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11078,19 +11078,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11187,32 +11187,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11220,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11244,17 +11248,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11264,17 +11268,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11302,32 +11306,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11335,7 +11343,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11359,17 +11367,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11379,17 +11387,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11417,32 +11425,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11450,7 +11462,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11474,17 +11486,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11494,17 +11506,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11532,32 +11544,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11565,7 +11581,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11589,17 +11605,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11609,12 +11625,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11647,32 +11663,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -11680,7 +11700,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11704,17 +11724,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11724,12 +11744,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11795,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11844,12 +11864,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11910,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11954,17 +11974,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
